--- a/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.2_Deletion_Methods_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.10-data-deletion/WKBK/90_workbooks/ISMS-IMP-A.8.10.2_Deletion_Methods_Assessment_20260208.xlsx
@@ -667,7 +667,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 FRAMEWORK OVERVIEW</t>
+          <t>NIST SP 800-88 Rev. 2 FRAMEWORK OVERVIEW</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ASSESSMENT QUESTION:
-Do we have effective deletion methods for all types of physical media, validated through testing, and aligned with NIST SP 800-88 guidance?</t>
+Do we have effective deletion methods for all types of physical media, validated through testing, and aligned with NIST SP 800-88 Rev. 2 guidance?</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 Method</t>
+          <t>NIST SP 800-88 Rev. 2 Method</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 method classification assigned (Clear/Purge/Destroy)</t>
+          <t>NIST SP 800-88 Rev. 2 method classification assigned (Clear/Purge/Destroy)</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr"/>
@@ -6447,7 +6447,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>NIST SP 800-88 METHOD DISTRIBUTION</t>
+          <t>NIST SP 800-88 Rev. 2 METHOD DISTRIBUTION</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="D5:D104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Deletion Tool Documentation,Forensic Test Report,Screenshot/Print Screen,System Log Export,Configuration File,Certificate of Destruction,Vendor Documentation,NIST SP 800-88 Compliance Memo,Test Result (Pass/Fail),Third-Party Audit Report,Other"</formula1>
+      <formula1>"Deletion Tool Documentation,Forensic Test Report,Screenshot/Print Screen,System Log Export,Configuration File,Certificate of Destruction,Vendor Documentation,NIST SP 800-88 Rev. 2 Compliance Memo,Test Result (Pass/Fail),Third-Party Audit Report,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sheet 2: Physical Storage Media,Sheet 3: Database Systems,Sheet 4: Cloud Storage,Sheet 5: File Systems &amp; Backup Media,Sheet 6: Deletion Verification Testing"</formula1>
